--- a/Excel_read_write/ex.xlsx
+++ b/Excel_read_write/ex.xlsx
@@ -1,33 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kavinda Ravishan\source\repos\Excel_read_write\Excel_read_write\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kavinda Ravishan\source\repos\kavinda-ravishan\Excel_read_write\Excel_read_write\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE196EBF-3CB6-42C2-9C5E-201F91BEB446}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF62AA74-CF88-48D8-8E9A-B9DD7F0E1CE1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1140" windowWidth="20490" windowHeight="9900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="870" windowWidth="20490" windowHeight="9900" xr2:uid="{5D255112-F3C3-4B9E-87CE-C60E130D7CC9}"/>
   </bookViews>
   <sheets>
-    <sheet name="s1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>hello kavinda</t>
+    <t>Wave Lenght</t>
+  </si>
+  <si>
+    <t>Power</t>
   </si>
 </sst>
 </file>
@@ -82,6 +91,1453 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="99"/>
+                <c:pt idx="0">
+                  <c:v>1540</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1541</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1542</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1543</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1544</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1545</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1546</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1547</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1548</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1549</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1550</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1551</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1552</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1553</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1554</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1555</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1556</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1557</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1558</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1559</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1560</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1561</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1562</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1563</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1564</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1565</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1566</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1567</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1568</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1569</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1570</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1571</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1572</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1573</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1574</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1575</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1576</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1577</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1578</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1579</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1580</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1581</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1582</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1583</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1584</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1585</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1586</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1587</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1588</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1589</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1590</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1591</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1592</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1593</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1594</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1595</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1596</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1597</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1598</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1599</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1601</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1602</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1603</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1604</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1605</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1606</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1607</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1608</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1609</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1610</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1611</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1612</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1613</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1614</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>1615</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>1616</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>1617</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>1618</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>1619</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>1620</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1621</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1622</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>1623</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>1624</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1625</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>1626</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>1627</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1628</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>1629</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>1630</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1631</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>1632</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>1633</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>1634</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1635</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1636</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1637</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1638</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="99"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E127-4EEF-93EC-47C2F54EA9C1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1296737760"/>
+        <c:axId val="1294408448"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1296737760"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1294408448"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1294408448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1296737760"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF703016-5DA0-46A2-AD1A-8F2AAC002931}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -99,7 +1555,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -111,7 +1567,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -158,6 +1614,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -193,6 +1666,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -344,61 +1834,812 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7C6077-7709-423C-8E4F-5241D6953E70}">
+  <dimension ref="A1:B100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1540</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1541</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1542</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1543</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1544</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1545</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1546</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1547</v>
+      </c>
+      <c r="B9">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1548</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1549</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1550</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1551</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1552</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1553</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1554</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1555</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1556</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1557</v>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1558</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1559</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1560</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1561</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1562</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1563</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1564</v>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1565</v>
+      </c>
+      <c r="B27">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>1566</v>
+      </c>
+      <c r="B28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1567</v>
+      </c>
+      <c r="B29">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1568</v>
+      </c>
+      <c r="B30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1569</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1570</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1571</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1572</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1573</v>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>1574</v>
+      </c>
+      <c r="B36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>1575</v>
+      </c>
+      <c r="B37">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>1576</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1577</v>
+      </c>
+      <c r="B39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1578</v>
+      </c>
+      <c r="B40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1579</v>
+      </c>
+      <c r="B41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1580</v>
+      </c>
+      <c r="B42">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>1581</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1582</v>
+      </c>
+      <c r="B44">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1583</v>
+      </c>
+      <c r="B45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1584</v>
+      </c>
+      <c r="B46">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1585</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1586</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1587</v>
+      </c>
+      <c r="B49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1588</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1589</v>
+      </c>
+      <c r="B51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1590</v>
+      </c>
+      <c r="B52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1591</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1592</v>
+      </c>
+      <c r="B54">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1593</v>
+      </c>
+      <c r="B55">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>1594</v>
+      </c>
+      <c r="B56">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1595</v>
+      </c>
+      <c r="B57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>1596</v>
+      </c>
+      <c r="B58">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1597</v>
+      </c>
+      <c r="B59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1598</v>
+      </c>
+      <c r="B60">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1599</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1600</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1601</v>
+      </c>
+      <c r="B63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>1602</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>1603</v>
+      </c>
+      <c r="B65">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1604</v>
+      </c>
+      <c r="B66">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1605</v>
+      </c>
+      <c r="B67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>1606</v>
+      </c>
+      <c r="B68">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1607</v>
+      </c>
+      <c r="B69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1608</v>
+      </c>
+      <c r="B70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>1609</v>
+      </c>
+      <c r="B71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>1610</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1611</v>
+      </c>
+      <c r="B73">
         <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>1612</v>
+      </c>
+      <c r="B74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>1613</v>
+      </c>
+      <c r="B75">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1614</v>
+      </c>
+      <c r="B76">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>1615</v>
+      </c>
+      <c r="B77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>1616</v>
+      </c>
+      <c r="B78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>1617</v>
+      </c>
+      <c r="B79">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>1618</v>
+      </c>
+      <c r="B80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>1619</v>
+      </c>
+      <c r="B81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>1620</v>
+      </c>
+      <c r="B82">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>1621</v>
+      </c>
+      <c r="B83">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>1622</v>
+      </c>
+      <c r="B84">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>1623</v>
+      </c>
+      <c r="B85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>1624</v>
+      </c>
+      <c r="B86">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1625</v>
+      </c>
+      <c r="B87">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>1626</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>1627</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>1628</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>1629</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>1630</v>
+      </c>
+      <c r="B92">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>1631</v>
+      </c>
+      <c r="B93">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>1632</v>
+      </c>
+      <c r="B94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>1633</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>1634</v>
+      </c>
+      <c r="B96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>1635</v>
+      </c>
+      <c r="B97">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>1636</v>
+      </c>
+      <c r="B98">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>1637</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>1638</v>
+      </c>
+      <c r="B100">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>